--- a/data/_master-data/fuel data.xlsx
+++ b/data/_master-data/fuel data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanj\GitHub\PhD\J4\data\master_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jujmo\Github\J4\data\_master-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2B7E71-A160-4D04-BC09-95CA4CAF474D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C469E0-8877-40E9-84B2-EDC47D375D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{6E05FBF9-7A0C-4B38-8AD0-297E8124D7D0}"/>
+    <workbookView xWindow="43200" yWindow="450" windowWidth="14400" windowHeight="17550" activeTab="1" xr2:uid="{6E05FBF9-7A0C-4B38-8AD0-297E8124D7D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="67">
   <si>
     <t>name</t>
   </si>
@@ -294,7 +294,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -304,6 +304,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -384,10 +390,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2696,9 +2702,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2736,7 +2742,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2842,7 +2848,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2984,7 +2990,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2993,15 +2999,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F84892A-CC8E-4DC7-9F4D-D8EB14D4CECE}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3012,7 +3018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3029,7 +3035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -3046,7 +3052,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E4" t="s">
         <v>12</v>
       </c>
@@ -3054,7 +3060,7 @@
         <v>23.653742261001035</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E5" t="s">
         <v>14</v>
       </c>
@@ -3062,7 +3068,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E6" t="s">
         <v>16</v>
       </c>
@@ -3070,7 +3076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -3087,7 +3093,7 @@
         <v>63.953800814148522</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -3104,7 +3110,7 @@
         <v>100.99632645054876</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -3121,7 +3127,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -3138,7 +3144,7 @@
         <v>66.775568974180501</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3155,7 +3161,7 @@
         <v>50.562577151316702</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -3172,7 +3178,7 @@
         <v>69.572960084315127</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E13" t="s">
         <v>15</v>
       </c>
@@ -3180,7 +3186,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C16" s="1">
         <v>97.723191022327597</v>
       </c>
@@ -3192,7 +3198,7 @@
         <v>100.99632645054876</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C17" s="1">
         <v>51.064117390840089</v>
       </c>
@@ -3204,7 +3210,7 @@
         <v>50.562577151316702</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C18">
         <v>67.268189007444789</v>
       </c>
@@ -3216,18 +3222,18 @@
         <v>69.572960084315127</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C22">
         <f>42.5*3.6</f>
         <v>153</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C25" s="11">
         <v>79.3</v>
       </c>
@@ -3247,16 +3253,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{931181A0-02B4-4BE8-AAB8-3DB7EDEE65B2}">
   <dimension ref="A1:O17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="10.7109375" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="10.7265625" customWidth="1"/>
+    <col min="8" max="12" width="10.7265625" customWidth="1"/>
+    <col min="13" max="14" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>30</v>
       </c>
@@ -3266,12 +3272,8 @@
       <c r="C1" t="s">
         <v>31</v>
       </c>
-      <c r="F1">
-        <f>175*B1/1000</f>
-        <v>2.3467500000000002E-2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -3282,7 +3284,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -3293,10 +3295,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B4" s="6"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B5" s="20" t="s">
         <v>48</v>
       </c>
@@ -3328,7 +3330,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16"/>
       <c r="B6" s="13" t="s">
         <v>18</v>
@@ -3348,32 +3350,32 @@
       <c r="G6" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I6" s="22" t="s">
+      <c r="I6" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J6" s="22" t="s">
+      <c r="J6" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="K6" s="22" t="s">
+      <c r="K6" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="L6" s="22" t="s">
+      <c r="L6" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="M6" s="22" t="s">
+      <c r="M6" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="N6" s="22" t="s">
+      <c r="N6" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="O6" s="22" t="s">
+      <c r="O6" s="13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>6</v>
       </c>
@@ -3405,28 +3407,29 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" t="s">
-        <v>65</v>
+        <v>57</v>
+      </c>
+      <c r="K7">
+        <f>39.6/1000</f>
+        <v>3.9600000000000003E-2</v>
       </c>
       <c r="L7" t="s">
-        <v>65</v>
-      </c>
-      <c r="M7" s="6">
-        <f>H7*$B$2*$B$1</f>
-        <v>4.7310480000000002E-2</v>
+        <v>59</v>
+      </c>
+      <c r="M7" s="23">
+        <f>H7*(1/K7)*$B$2*$B$1</f>
+        <v>1.1947090909090907</v>
       </c>
       <c r="N7" s="6">
-        <f>I7*$B$2*$B$1</f>
+        <f>I7*(1/K7)*$B$2*$B$1</f>
         <v>0</v>
       </c>
-      <c r="O7" s="6">
+      <c r="O7" s="5">
         <f>M7+N7</f>
-        <v>4.7310480000000002E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1.1947090909090907</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>12</v>
       </c>
@@ -3474,12 +3477,12 @@
         <f>I8*$B$2*$B$1</f>
         <v>8.1103680000000011</v>
       </c>
-      <c r="O8" s="7">
+      <c r="O8" s="5">
         <f t="shared" ref="O8:O17" si="3">M8+N8</f>
         <v>35.482860000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>14</v>
       </c>
@@ -3498,7 +3501,7 @@
       <c r="F9">
         <v>175</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="22">
         <f t="shared" si="2"/>
         <v>2.3467500000000002E-2</v>
       </c>
@@ -3525,12 +3528,12 @@
         <f>I9*$B$1</f>
         <v>0</v>
       </c>
-      <c r="O9" s="7">
+      <c r="O9" s="5">
         <f t="shared" si="3"/>
         <v>11.96172</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>16</v>
       </c>
@@ -3576,12 +3579,12 @@
       <c r="N10" s="6">
         <v>0</v>
       </c>
-      <c r="O10" s="7">
+      <c r="O10" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>10</v>
       </c>
@@ -3629,12 +3632,12 @@
         <f>I11/K11*$B$2*$B$1</f>
         <v>6.6624442804428048</v>
       </c>
-      <c r="O11" s="7">
+      <c r="O11" s="5">
         <f t="shared" si="3"/>
         <v>34.048534317343169</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>11</v>
       </c>
@@ -3682,12 +3685,12 @@
         <f>I12/B3*1000*(1/K12)*$B$2*$B$1</f>
         <v>6.3124355971896957</v>
       </c>
-      <c r="O12" s="7">
+      <c r="O12" s="5">
         <f t="shared" si="3"/>
         <v>33.702214787554361</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
         <v>13</v>
       </c>
@@ -3733,12 +3736,12 @@
       <c r="N13" s="6">
         <v>0</v>
       </c>
-      <c r="O13" s="7">
+      <c r="O13" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
         <v>7</v>
       </c>
@@ -3772,7 +3775,7 @@
       <c r="J14" t="s">
         <v>57</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="5">
         <f>39.59/1000</f>
         <v>3.959E-2</v>
       </c>
@@ -3787,12 +3790,12 @@
         <f>I14*(1/K14)*$B$2*$B$1</f>
         <v>4.8775953523617082</v>
       </c>
-      <c r="O14" s="7">
+      <c r="O14" s="5">
         <f t="shared" si="3"/>
         <v>32.265293255872692</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>9</v>
       </c>
@@ -3838,12 +3841,12 @@
       <c r="N15" s="6">
         <v>0</v>
       </c>
-      <c r="O15" s="7">
+      <c r="O15" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>8</v>
       </c>
@@ -3889,12 +3892,12 @@
       <c r="N16" s="6">
         <v>0</v>
       </c>
-      <c r="O16" s="7">
+      <c r="O16" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>15</v>
       </c>
@@ -3940,7 +3943,7 @@
       <c r="N17" s="15">
         <v>0</v>
       </c>
-      <c r="O17" s="23">
+      <c r="O17" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3972,13 +3975,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51230364-8773-4F67-A6EA-CD39F2C43C63}">
   <dimension ref="A1:E62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="15.7265625" customWidth="1"/>
+    <col min="3" max="3" width="17.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -3992,7 +3995,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -4004,7 +4007,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -4018,7 +4021,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -4029,7 +4032,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -4040,7 +4043,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -4051,7 +4054,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -4063,22 +4066,22 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B8" s="6"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B9" s="6"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B10" s="6"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B11" s="6"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B12" s="6"/>
     </row>
-    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>19</v>
       </c>
@@ -4089,7 +4092,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>3.4808400000000003E-2</v>
       </c>
@@ -4101,7 +4104,7 @@
         <v>77.171474914585204</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>0.26686440000000011</v>
       </c>
@@ -4114,7 +4117,7 @@
       </c>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>0.26686440000000011</v>
       </c>
@@ -4126,7 +4129,7 @@
         <v>75.090106763486304</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>0.53373276000000014</v>
       </c>
@@ -4138,7 +4141,7 @@
         <v>75.090106763486304</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>1.5081264000000001</v>
       </c>
@@ -4150,7 +4153,7 @@
         <v>75.090106763486304</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>1.9099476</v>
       </c>
@@ -4162,7 +4165,7 @@
         <v>75.090106763486304</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>2.0477159999999999</v>
       </c>
@@ -4174,7 +4177,7 @@
         <v>75.090106763486304</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>2.6486063999999998</v>
       </c>
@@ -4186,7 +4189,7 @@
         <v>75.090106763486304</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>2.6486063999999998</v>
       </c>
@@ -4198,7 +4201,7 @@
         <v>75.090106763486304</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>2.6809992</v>
       </c>
@@ -4210,7 +4213,7 @@
         <v>75.090106763486304</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>2.8805040000000002</v>
       </c>
@@ -4222,7 +4225,7 @@
         <v>75.090106763486304</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>3.0080952000000001</v>
       </c>
@@ -4234,7 +4237,7 @@
         <v>72.516119090521897</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>3.0322908000000002</v>
       </c>
@@ -4246,7 +4249,7 @@
         <v>72.516119090521897</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>3.6152820000000001</v>
       </c>
@@ -4258,7 +4261,7 @@
         <v>72.516119090521897</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>4.2768792000000007</v>
       </c>
@@ -4270,7 +4273,7 @@
         <v>72.516119090521897</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>6.0011424000000009</v>
       </c>
@@ -4282,7 +4285,7 @@
         <v>72.516119090521897</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>6.4308024000000001</v>
       </c>
@@ -4294,7 +4297,7 @@
         <v>72.516119090521897</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>7.1992800000000008</v>
       </c>
@@ -4306,7 +4309,7 @@
         <v>72.516119090521897</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>7.8408000000000007</v>
       </c>
@@ -4318,7 +4321,7 @@
         <v>72.516119090521897</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>8.342254800000001</v>
       </c>
@@ -4330,7 +4333,7 @@
         <v>72.516119090521897</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>10.814205599999999</v>
       </c>
@@ -4342,7 +4345,7 @@
         <v>72.516119090521897</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>11.4417072</v>
       </c>
@@ -4354,7 +4357,7 @@
         <v>72.516119090521897</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>13.255307999999999</v>
       </c>
@@ -4366,7 +4369,7 @@
         <v>67.671424624389005</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>14.081900603999999</v>
       </c>
@@ -4378,7 +4381,7 @@
         <v>67.671424624389005</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>14.250733200000001</v>
       </c>
@@ -4390,7 +4393,7 @@
         <v>67.671424624389005</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>14.445327600000001</v>
       </c>
@@ -4402,7 +4405,7 @@
         <v>67.671424624389005</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>14.8172508</v>
       </c>
@@ -4414,7 +4417,7 @@
         <v>67.671424624389005</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>17.1024876</v>
       </c>
@@ -4426,7 +4429,7 @@
         <v>67.671424624389005</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
         <v>17.220178799999999</v>
       </c>
@@ -4438,7 +4441,7 @@
         <v>67.671424624389005</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="5">
         <v>20.295475199999998</v>
       </c>
@@ -4450,7 +4453,7 @@
         <v>67.671424624389005</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
         <v>21.0055032</v>
       </c>
@@ -4462,7 +4465,7 @@
         <v>67.671424624389005</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
         <v>21.452626800000001</v>
       </c>
@@ -4474,7 +4477,7 @@
         <v>67.671424624389005</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="5">
         <v>23.572454400000002</v>
       </c>
@@ -4486,7 +4489,7 @@
         <v>67.671424624389005</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
         <v>26.008606799999999</v>
       </c>
@@ -4498,7 +4501,7 @@
         <v>67.671424624389005</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="5">
         <v>26.070739199999998</v>
       </c>
@@ -4510,7 +4513,7 @@
         <v>67.671424624389005</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="5">
         <v>32.545972800000001</v>
       </c>
@@ -4522,7 +4525,7 @@
         <v>66.775568974180501</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="5">
         <v>34.686669600000002</v>
       </c>
@@ -4534,7 +4537,7 @@
         <v>66.775568974180501</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="5">
         <v>40.807839600000008</v>
       </c>
@@ -4546,7 +4549,7 @@
         <v>66.775568974180501</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="5">
         <v>59.171389200000007</v>
       </c>
@@ -4558,7 +4561,7 @@
         <v>66.775568974180501</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="5">
         <v>67.955976000000007</v>
       </c>
@@ -4570,7 +4573,7 @@
         <v>66.775568974180501</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="5">
         <v>69.373339200000004</v>
       </c>
@@ -4582,7 +4585,7 @@
         <v>66.775568974180501</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="5">
         <v>155.0458404</v>
       </c>
@@ -4594,7 +4597,7 @@
         <v>66.775568974180501</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="5">
         <v>172.63227128400001</v>
       </c>
@@ -4606,7 +4609,7 @@
         <v>66.775568974180501</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="5">
         <v>225.70555431599999</v>
       </c>
@@ -4618,7 +4621,7 @@
         <v>66.775568974180501</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="5">
         <v>336.30921719999998</v>
       </c>
@@ -4630,7 +4633,7 @@
         <v>66.775568974180501</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="5">
         <v>435.31792919999998</v>
       </c>
@@ -4642,7 +4645,7 @@
         <v>65.729483845677706</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="5">
         <v>816.32984400000009</v>
       </c>
@@ -4660,7 +4663,7 @@
     <sortCondition ref="A16:A62"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/_master-data/fuel data.xlsx
+++ b/data/_master-data/fuel data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jujmo\Github\J4\data\_master-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C469E0-8877-40E9-84B2-EDC47D375D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFBFAB5-9DF9-4C10-BD5A-9906F5E10171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43200" yWindow="450" windowWidth="14400" windowHeight="17550" activeTab="1" xr2:uid="{6E05FBF9-7A0C-4B38-8AD0-297E8124D7D0}"/>
+    <workbookView xWindow="28680" yWindow="330" windowWidth="29040" windowHeight="17790" activeTab="1" xr2:uid="{6E05FBF9-7A0C-4B38-8AD0-297E8124D7D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="68">
   <si>
     <t>name</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>Total tax</t>
+  </si>
+  <si>
+    <t>Total cost</t>
   </si>
 </sst>
 </file>
@@ -384,16 +387,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3252,7 +3255,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{931181A0-02B4-4BE8-AAB8-3DB7EDEE65B2}">
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.7265625" bestFit="1" customWidth="1"/>
@@ -3260,9 +3263,10 @@
     <col min="8" max="12" width="10.7265625" customWidth="1"/>
     <col min="13" max="14" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>30</v>
       </c>
@@ -3273,7 +3277,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -3284,7 +3288,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -3295,31 +3299,31 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B4" s="6"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B5" s="20" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B5" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="21" t="s">
+      <c r="C5" s="22"/>
+      <c r="D5" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21" t="s">
+      <c r="E5" s="23"/>
+      <c r="F5" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21" t="s">
+      <c r="G5" s="23"/>
+      <c r="H5" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21" t="s">
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="21"/>
+      <c r="L5" s="23"/>
       <c r="M5" s="19" t="s">
         <v>53</v>
       </c>
@@ -3329,8 +3333,11 @@
       <c r="O5" s="19" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P5" s="19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16"/>
       <c r="B6" s="13" t="s">
         <v>18</v>
@@ -3375,7 +3382,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>6</v>
       </c>
@@ -3416,7 +3423,7 @@
       <c r="L7" t="s">
         <v>59</v>
       </c>
-      <c r="M7" s="23">
+      <c r="M7" s="21">
         <f>H7*(1/K7)*$B$2*$B$1</f>
         <v>1.1947090909090907</v>
       </c>
@@ -3428,8 +3435,12 @@
         <f>M7+N7</f>
         <v>1.1947090909090907</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P7" s="7">
+        <f>C7+O7+E7*G7</f>
+        <v>81.590043712551548</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>12</v>
       </c>
@@ -3481,8 +3492,12 @@
         <f t="shared" ref="O8:O17" si="3">M8+N8</f>
         <v>35.482860000000002</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P8" s="7">
+        <f t="shared" ref="P8:P17" si="4">C8+O8+E8*G8</f>
+        <v>52.257949480754391</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>14</v>
       </c>
@@ -3501,7 +3516,7 @@
       <c r="F9">
         <v>175</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="20">
         <f t="shared" si="2"/>
         <v>2.3467500000000002E-2</v>
       </c>
@@ -3532,8 +3547,12 @@
         <f t="shared" si="3"/>
         <v>11.96172</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P9" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>16</v>
       </c>
@@ -3583,8 +3602,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P10" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>10</v>
       </c>
@@ -3636,8 +3659,12 @@
         <f t="shared" si="3"/>
         <v>34.048534317343169</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P11" s="7">
+        <f t="shared" si="4"/>
+        <v>70.339035219790446</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>11</v>
       </c>
@@ -3689,8 +3716,12 @@
         <f t="shared" si="3"/>
         <v>33.702214787554361</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P12" s="7">
+        <f t="shared" si="4"/>
+        <v>87.181160687554367</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
         <v>13</v>
       </c>
@@ -3740,8 +3771,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P13" s="7">
+        <f t="shared" si="4"/>
+        <v>-16.106080499999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
         <v>7</v>
       </c>
@@ -3794,8 +3829,12 @@
         <f t="shared" si="3"/>
         <v>32.265293255872692</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P14" s="7">
+        <f t="shared" si="4"/>
+        <v>58.766277682350221</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>9</v>
       </c>
@@ -3845,8 +3884,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P15" s="7">
+        <f t="shared" si="4"/>
+        <v>25.8614532</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>8</v>
       </c>
@@ -3896,8 +3939,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P16" s="7">
+        <f t="shared" si="4"/>
+        <v>34.918030800000004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>15</v>
       </c>
@@ -3946,6 +3993,10 @@
       <c r="O17" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
+      </c>
+      <c r="P17" s="7">
+        <f t="shared" si="4"/>
+        <v>12.069000000000001</v>
       </c>
     </row>
   </sheetData>
